--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487107_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487107_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6716</v>
+        <v>3.502</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6679</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0037</v>
+        <v>2.6557</v>
       </c>
       <c r="G2" t="n">
         <v>3.2978</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7053</v>
+        <v>0.5357</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0317</v>
+        <v>0.1468</v>
       </c>
       <c r="U2" t="n">
-        <v>0.737</v>
+        <v>0.389</v>
       </c>
       <c r="V2" t="n">
         <v>0.2476</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.343</v>
+        <v>2.9835</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7205</v>
+        <v>2.0398</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.9437</v>
       </c>
       <c r="G3" t="n">
         <v>4.7374</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6623</v>
+        <v>-0.0218</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3886</v>
+        <v>-0.0694</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2737</v>
+        <v>0.0476</v>
       </c>
       <c r="V3" t="n">
         <v>0.7771</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.117</v>
+        <v>1.1973</v>
       </c>
       <c r="E4" t="n">
         <v>0.4839</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6331</v>
+        <v>0.7134</v>
       </c>
       <c r="G4" t="n">
         <v>1.2565</v>
@@ -766,13 +766,13 @@
         <v>0.386</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5255</v>
+        <v>-0.4452</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0616</v>
+        <v>0.105</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7125</v>
+        <v>-0.6531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.651</v>
+        <v>0.758</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3405</v>
@@ -844,13 +844,13 @@
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1071</v>
+        <v>0.0595</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0449</v>
+        <v>0.0145</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0621</v>
+        <v>0.0449</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1894</v>
+        <v>-0.0764</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6957</v>
+        <v>-1.6362</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5063</v>
+        <v>1.5598</v>
       </c>
       <c r="G6" t="n">
         <v>0.502</v>
@@ -922,13 +922,13 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3054</v>
+        <v>-0.1924</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1044</v>
+        <v>-0.0449</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.201</v>
+        <v>-0.1474</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3564</v>
+        <v>-1.5163</v>
       </c>
       <c r="E7" t="n">
-        <v>1.804</v>
+        <v>-2.858</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1603</v>
+        <v>1.3416</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.169</v>
+        <v>0.8678</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.8526</v>
+        <v>1.6789</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6836</v>
+        <v>-0.8111</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.549</v>
+        <v>0.3402</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.6654</v>
+        <v>1.1385</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1164</v>
+        <v>-0.7983</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6199</v>
+        <v>0.5276</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1872</v>
+        <v>0.5404</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4327</v>
+        <v>-0.0129</v>
       </c>
       <c r="P7" t="n">
-        <v>0.193</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-3.0881</v>
       </c>
       <c r="R7" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5421</v>
+        <v>-0.2261</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0901</v>
+        <v>-0.11</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.548</v>
+        <v>-0.116</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.9225</v>
+        <v>-0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.1505</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.554</v>
+        <v>-1.8236</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1366</v>
+        <v>-1.9972</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5826</v>
+        <v>0.1736</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8678</v>
+        <v>-0.6575</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6789</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8111</v>
+        <v>-1.3788</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3402</v>
+        <v>0.8167</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1385</v>
+        <v>1.2158</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7983</v>
+        <v>-0.3991</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5276</v>
+        <v>-1.4742</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5404</v>
+        <v>-0.4945</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0129</v>
+        <v>-0.9797</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5441</v>
+        <v>-0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0881</v>
+        <v>-2.1231</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2637</v>
+        <v>0.4901</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3886</v>
+        <v>0.2935</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1249</v>
+        <v>0.1966</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.614</v>
+        <v>-1.2702</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.9843</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9336</v>
+        <v>-2.0016</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2947</v>
+        <v>-1.4428</v>
       </c>
       <c r="F9" t="n">
-        <v>0.361</v>
+        <v>-0.5588</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6575</v>
+        <v>-1.8393</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7213000000000001</v>
+        <v>-1.2481</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3788</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8167</v>
+        <v>-1.1325</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2158</v>
+        <v>-1.1075</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3991</v>
+        <v>-0.025</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4742</v>
+        <v>-0.7068</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4945</v>
+        <v>-0.1406</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9797</v>
+        <v>-0.5662</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.386</v>
+        <v>1.7371</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1231</v>
+        <v>-0.193</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3801</v>
+        <v>-0.2628</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0039</v>
+        <v>-0.1173</v>
       </c>
       <c r="U9" t="n">
-        <v>0.384</v>
+        <v>-0.1455</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2702</v>
+        <v>-1.6366</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.9843</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>-1.6366</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.492</v>
+        <v>-2.2378</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4835</v>
+        <v>0.521</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9915</v>
+        <v>-2.7588</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4868</v>
+        <v>-1.169</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0052</v>
+        <v>-2.8526</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4816</v>
+        <v>1.6836</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6407</v>
+        <v>-0.549</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3055</v>
+        <v>-2.6654</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3352</v>
+        <v>2.1164</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1539</v>
+        <v>-0.6199</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3002</v>
+        <v>-0.1872</v>
       </c>
       <c r="O10" t="n">
+        <v>-0.4327</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6607</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.8071</v>
+      </c>
+      <c r="U10" t="n">
         <v>-0.1464</v>
       </c>
-      <c r="P10" t="n">
-        <v>-0.579</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1.9301</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3511</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.3034</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.0873</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.3907</v>
-      </c>
       <c r="V10" t="n">
-        <v>-0.1228</v>
+        <v>-1.9225</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1228</v>
+        <v>-3.1505</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6074</v>
+        <v>-2.3929</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2627</v>
+        <v>-3.4647</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3447</v>
+        <v>1.0718</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8393</v>
+        <v>-1.4868</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2481</v>
+        <v>-0.0052</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-1.4816</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1325</v>
+        <v>-1.6407</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1075</v>
+        <v>-0.3055</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.025</v>
+        <v>-1.3352</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7068</v>
+        <v>0.1539</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1406</v>
+        <v>0.3002</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5662</v>
+        <v>-0.1464</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7371</v>
+        <v>-0.579</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.193</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8686</v>
+        <v>-0.2042</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9373</v>
+        <v>0.1061</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0687</v>
+        <v>-0.3104</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6366</v>
+        <v>-0.1228</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6366</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.4506</v>
+        <v>-7.7655</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8158</v>
+        <v>-5.0772</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6348</v>
+        <v>-2.6883</v>
       </c>
       <c r="G12" t="n">
         <v>-1.498</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6293</v>
+        <v>0.0559</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6411</v>
+        <v>0.0975</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0119</v>
+        <v>-0.0417</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8842</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.5134</v>
+        <v>-10.0263</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.7252</v>
+        <v>-13.2382</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2119</v>
+        <v>3.2117</v>
       </c>
       <c r="G13" t="n">
         <v>3.670400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9679999999999997</v>
+        <v>0.9680000000000002</v>
       </c>
       <c r="I13" t="n">
         <v>2.702500000000001</v>
@@ -1444,13 +1444,13 @@
         <v>4.432399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4979999999999996</v>
+        <v>-0.4980000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>4.9304</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7618999999999999</v>
+        <v>-0.7618999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>1.4659</v>
@@ -1468,22 +1468,22 @@
         <v>13.5107</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0378</v>
+        <v>0.4493999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5416000000000001</v>
+        <v>0.9454</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.496</v>
+        <v>-0.4960000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.425599999999999</v>
+        <v>-6.4256</v>
       </c>
       <c r="W13" t="n">
         <v>2.6151</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.040799999999999</v>
+        <v>-9.040800000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8192</v>
+        <v>7.6941</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8618</v>
+        <v>4.3625</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9574</v>
+        <v>3.3316</v>
       </c>
       <c r="G14" t="n">
         <v>1.0613</v>
@@ -1546,13 +1546,13 @@
         <v>3.6672</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8487</v>
+        <v>0.0261</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.805</v>
+        <v>-0.3043</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0437</v>
+        <v>0.3304</v>
       </c>
       <c r="V14" t="n">
         <v>4.8696</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9352</v>
+        <v>4.0627</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1428</v>
+        <v>1.8424</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7924</v>
+        <v>2.2203</v>
       </c>
       <c r="G15" t="n">
         <v>3.1757</v>
@@ -1624,13 +1624,13 @@
         <v>2.8951</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2056</v>
+        <v>-0.078</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3979</v>
+        <v>0.0975</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6035</v>
+        <v>-0.1755</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6602</v>
+        <v>1.4721</v>
       </c>
       <c r="E16" t="n">
         <v>-1.4616</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1218</v>
+        <v>2.9338</v>
       </c>
       <c r="G16" t="n">
         <v>3.5198</v>
@@ -1702,13 +1702,13 @@
         <v>3.6672</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6339</v>
+        <v>0.4458</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1374</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7713</v>
+        <v>0.5833</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3704</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>P. OSES TOME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5092</v>
+        <v>0.9404</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3752</v>
+        <v>-0.0988</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8844</v>
+        <v>1.0392</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2066</v>
+        <v>-0.2583</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4606</v>
+        <v>-0.9274</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6672</v>
+        <v>0.669</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5074</v>
+        <v>-0.2717</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2536</v>
+        <v>-0.2795</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2538</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3008</v>
+        <v>0.0134</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7141999999999999</v>
+        <v>-0.6478</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4134</v>
+        <v>0.6612</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2915</v>
+        <v>0.2337</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1322</v>
+        <v>0.1729</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4237</v>
+        <v>0.0608</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARBIZU MAIZA</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4759</v>
+        <v>0.7299</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0081</v>
+        <v>-1.4754</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4839</v>
+        <v>2.2053</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0937</v>
+        <v>-1.2066</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5349</v>
+        <v>0.4606</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4413</v>
+        <v>-1.6672</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2738</v>
+        <v>-1.5074</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3145</v>
+        <v>-0.2536</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0407</v>
+        <v>-1.2538</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1801</v>
+        <v>0.3008</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2204</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4006</v>
+        <v>-0.4134</v>
       </c>
       <c r="P18" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6973</v>
+        <v>-0.0707</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2657</v>
+        <v>0.0321</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4316</v>
+        <v>-0.1028</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. OSES TOME</t>
+          <t>A. ARBIZU MAIZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1991</v>
+        <v>0.2753</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5995</v>
+        <v>-1.2084</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7986</v>
+        <v>1.4836</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2583</v>
+        <v>-1.0937</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9274</v>
+        <v>-1.5349</v>
       </c>
       <c r="I19" t="n">
-        <v>0.669</v>
+        <v>0.4413</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2717</v>
+        <v>-1.2738</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2795</v>
+        <v>-1.3145</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0134</v>
+        <v>0.1801</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6478</v>
+        <v>-0.2204</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6612</v>
+        <v>0.4006</v>
       </c>
       <c r="P19" t="n">
-        <v>0.965</v>
+        <v>1.158</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.965</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.4967</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3278</v>
+        <v>0.0655</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1798</v>
+        <v>0.4313</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1514</v>
+        <v>-0.0225</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7846</v>
+        <v>-0.9849</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9624</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4387</v>
@@ -2014,13 +2014,13 @@
         <v>2.8951</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3741</v>
+        <v>0.2003</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1455</v>
+        <v>-0.0548</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2287</v>
+        <v>0.2551</v>
       </c>
       <c r="V20" t="n">
         <v>0.2859</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0268</v>
+        <v>-0.3195</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.447</v>
+        <v>0.216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4201</v>
+        <v>-0.5355</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1557</v>
+        <v>-1.0281</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.8462</v>
+        <v>0.0187</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6904</v>
+        <v>-1.0468</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5288</v>
+        <v>0.4133</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.245</v>
+        <v>0.3726</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6269</v>
+        <v>-1.4414</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6012</v>
+        <v>-0.3539</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0257</v>
+        <v>-1.0875</v>
       </c>
       <c r="P21" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8937</v>
+        <v>-0.0635</v>
       </c>
       <c r="T21" t="n">
-        <v>0.591</v>
+        <v>-0.1973</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3027</v>
+        <v>0.1338</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2702</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3925</v>
+        <v>-0.3342</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7293</v>
+        <v>-0.6472</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3368</v>
+        <v>0.3131</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9233</v>
+        <v>-3.1557</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6562</v>
+        <v>-3.8462</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.267</v>
+        <v>0.6904</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0299</v>
+        <v>-2.5288</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3623</v>
+        <v>-3.245</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6676</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1067</v>
+        <v>-0.6269</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2939</v>
+        <v>-0.6012</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4006</v>
+        <v>-0.0257</v>
       </c>
       <c r="P22" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3378</v>
+        <v>0.5863</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2657</v>
+        <v>0.3907</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1956</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2702</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5</v>
+        <v>-0.3859</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1158</v>
+        <v>-1.8294</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6158</v>
+        <v>1.4435</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0281</v>
+        <v>-0.9233</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0187</v>
+        <v>-0.6562</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0468</v>
+        <v>-0.267</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4133</v>
+        <v>-1.0299</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3726</v>
+        <v>-0.3623</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0407</v>
+        <v>-0.6676</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4414</v>
+        <v>0.1067</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3539</v>
+        <v>-0.2939</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0875</v>
+        <v>0.4006</v>
       </c>
       <c r="P23" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2439</v>
+        <v>0.3444</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2974</v>
+        <v>0.1656</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0535</v>
+        <v>0.1788</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. ECHEONDO LACALLE</t>
+          <t>G. AZANZA TERUEL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5097</v>
+        <v>-0.5608</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5537</v>
+        <v>-0.7871</v>
       </c>
       <c r="F24" t="n">
-        <v>0.044</v>
+        <v>0.2263</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9367</v>
+        <v>-0.386</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2037</v>
+        <v>-0.386</v>
       </c>
       <c r="I24" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9833</v>
+        <v>0.0414</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9833</v>
+        <v>0.0414</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0466</v>
+        <v>-0.4274</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2204</v>
+        <v>-0.4274</v>
       </c>
       <c r="O24" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R24" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S24" t="n">
-        <v>0.234</v>
+        <v>0.2112</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4297</v>
+        <v>0.1365</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1957</v>
+        <v>0.0747</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. AZANZA TERUEL</t>
+          <t>I. ECHEONDO LACALLE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8077</v>
+        <v>-0.703</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0876</v>
+        <v>-0.8541</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2798</v>
+        <v>0.1511</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.386</v>
+        <v>-0.9367</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.386</v>
+        <v>-1.2037</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0414</v>
+        <v>-0.9833</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0414</v>
+        <v>-0.9833</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4274</v>
+        <v>0.0466</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4274</v>
+        <v>-0.2204</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.579</v>
+        <v>0.193</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0357</v>
+        <v>0.0407</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1639</v>
+        <v>0.1292</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1282</v>
+        <v>-0.0886</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,40 +2437,40 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11.5135</v>
+        <v>12.8486</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.926200000000001</v>
+        <v>-2.925999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>14.4394</v>
+        <v>15.7747</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.670300000000001</v>
+        <v>-3.6703</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9677999999999997</v>
+        <v>-0.9677999999999993</v>
       </c>
       <c r="I26" t="n">
         <v>-2.702600000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0.762</v>
+        <v>0.762000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>-1.4658</v>
       </c>
       <c r="L26" t="n">
-        <v>2.227900000000001</v>
+        <v>2.2279</v>
       </c>
       <c r="M26" t="n">
         <v>-4.432500000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4981000000000001</v>
+        <v>0.4980999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.9304</v>
+        <v>-4.930399999999999</v>
       </c>
       <c r="P26" t="n">
         <v>7.720199999999999</v>
@@ -2482,13 +2482,13 @@
         <v>21.2308</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0378</v>
+        <v>2.373</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4961999999999999</v>
+        <v>0.4962</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5416</v>
+        <v>1.8769</v>
       </c>
       <c r="V26" t="n">
         <v>6.4256</v>
